--- a/modelling/wsf grondwaterstroming/Properties_calculator.xlsx
+++ b/modelling/wsf grondwaterstroming/Properties_calculator.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Gitclones\FusionFiber\modelling\wsf grondwaterstroming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{012190B6-7363-4BCB-B6D4-27518E579325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A5E89D-9978-40EF-B581-F2AB60EB0B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{3632657A-28F7-4C1C-ABB4-32E130E65C30}"/>
+    <workbookView xWindow="-4956" yWindow="-21708" windowWidth="38616" windowHeight="21096" xr2:uid="{3632657A-28F7-4C1C-ABB4-32E130E65C30}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="60">
   <si>
     <t>n</t>
   </si>
@@ -117,16 +117,159 @@
   </si>
   <si>
     <t>bulk volumetric heat capacity</t>
+  </si>
+  <si>
+    <t>voltage</t>
+  </si>
+  <si>
+    <t>current</t>
+  </si>
+  <si>
+    <t>power</t>
+  </si>
+  <si>
+    <t>delta T</t>
+  </si>
+  <si>
+    <t>gw100</t>
+  </si>
+  <si>
+    <t>gw101</t>
+  </si>
+  <si>
+    <t>gw102</t>
+  </si>
+  <si>
+    <t>gw103</t>
+  </si>
+  <si>
+    <t>gw104</t>
+  </si>
+  <si>
+    <t>gw105</t>
+  </si>
+  <si>
+    <t>gw106</t>
+  </si>
+  <si>
+    <t>gw107</t>
+  </si>
+  <si>
+    <t>4pi</t>
+  </si>
+  <si>
+    <t>t1</t>
+  </si>
+  <si>
+    <t>t2</t>
+  </si>
+  <si>
+    <t>ln(t2/t1)</t>
+  </si>
+  <si>
+    <t>themal conductivity</t>
+  </si>
+  <si>
+    <t>test_id</t>
+  </si>
+  <si>
+    <t>L_heat</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- </t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>W/m/K?</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>W/m</t>
+  </si>
+  <si>
+    <t>all wrong</t>
+  </si>
+  <si>
+    <t>ohm/m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R' </t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>ohm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -152,13 +295,419 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="26">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -169,6 +718,66 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{ADD14A65-3CC2-47DC-BD41-E5B04B08ED26}" name="Table1" displayName="Table1" ref="A18:L27" totalsRowShown="0" headerRowDxfId="2" dataDxfId="1">
+  <autoFilter ref="A18:L27" xr:uid="{ADD14A65-3CC2-47DC-BD41-E5B04B08ED26}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{5E3D2BCB-EC8D-4572-9893-B19CF83CF613}" name="test_id" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{51100845-C0A2-4E71-A332-2D3FBC264EE5}" name="voltage" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{C210A0F9-C325-48B5-BECD-0EA8142E4CB8}" name="current" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{B2A9C5D3-2651-4183-BAC3-353109AC77F1}" name="power" dataDxfId="11">
+      <calculatedColumnFormula>B19*C19</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{F9E856D5-69F4-4695-AB1C-DB9CC68B1080}" name="L_heat" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{8088FFE0-4EC8-4010-9E5D-32D92B9724E5}" name="Q" dataDxfId="9">
+      <calculatedColumnFormula>D19/E19</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{749E0988-5F8A-431D-9759-B1C44812C2FF}" name="4pi" dataDxfId="8">
+      <calculatedColumnFormula>4*PI()</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{E258EE88-5073-4976-BEB5-BCAB4E6CE986}" name="delta T" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{4F541334-0B47-4F5A-8E94-823A36DE1DC3}" name="t1" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{D453985D-2954-4900-ABE6-3B7D92D6C1DA}" name="t2" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{5878AD62-191D-4951-9EDD-F6E1C8D1654F}" name="ln(t2/t1)" dataDxfId="4">
+      <calculatedColumnFormula>LN(J19/I19)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{CAD6440C-D430-4128-B544-44F61AA11D25}" name="themal conductivity" dataDxfId="3">
+      <calculatedColumnFormula>(F19/(G19*H19))*K19</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{14413E9C-D3BC-469C-AFBA-D7793CCD3051}" name="Table13" displayName="Table13" ref="A31:L40" totalsRowShown="0" headerRowDxfId="25">
+  <autoFilter ref="A31:L40" xr:uid="{14413E9C-D3BC-469C-AFBA-D7793CCD3051}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{64E88E43-5206-4027-BDAE-A5F8805B00CF}" name="test_id"/>
+    <tableColumn id="2" xr3:uid="{CF88E80E-BAC6-4641-9545-9C624AA4F792}" name="voltage" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{E2F2D6D4-FD7E-4CE4-80B6-8F482E6E1094}" name="R' " dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{9E02D136-963E-481F-9ED5-335BBA71D8F0}" name="L_heat" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{E536B8C0-C0B7-4A02-8311-D758ADD282CF}" name="R" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{6EA2D111-3F7A-4738-85F7-A6E6D9EC4081}" name="Q" dataDxfId="21">
+      <calculatedColumnFormula>#REF!/D32</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{CC757BB1-4AA7-4BA8-B48F-6F5E73B48840}" name="4pi" dataDxfId="20">
+      <calculatedColumnFormula>4*PI()</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{FDE5B33B-B9B1-4A21-818A-E99692FC8770}" name="delta T" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{7F3B899A-BBB7-43B4-82C7-C03DDBAED540}" name="t1" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{4FD5B21F-8D5F-4DD4-9DF8-B7C4003BBBBF}" name="t2" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{0E9D6543-0BD4-44EA-BC52-6EF7A9801AE7}" name="ln(t2/t1)" dataDxfId="16">
+      <calculatedColumnFormula>LN(J32/I32)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{2273EBAF-9CCB-4689-B4E0-67B7636BF857}" name="themal conductivity" dataDxfId="15">
+      <calculatedColumnFormula>(F32/(G32*H32))*K32</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -488,8 +1097,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE086DA3-B7D9-4EBD-B1A4-5E6F632602CC}">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="11" max="11" width="9.77734375" customWidth="1"/>
+    <col min="12" max="12" width="22.33203125" customWidth="1"/>
+    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.88671875" customWidth="1"/>
+    <col min="28" max="28" width="16.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -609,6 +1225,10 @@
       <c r="A11" t="s">
         <v>21</v>
       </c>
+      <c r="B11">
+        <f>B6*B1+(1-B6)*B7</f>
+        <v>1973.0900000000001</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -649,7 +1269,865 @@
         <v>23</v>
       </c>
     </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="6">
+        <v>230</v>
+      </c>
+      <c r="C20" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="D20" s="6">
+        <f>B20*C20</f>
+        <v>575</v>
+      </c>
+      <c r="E20" s="6">
+        <v>64</v>
+      </c>
+      <c r="F20" s="11">
+        <f>D20/E20</f>
+        <v>8.984375</v>
+      </c>
+      <c r="G20" s="11">
+        <f>4*PI()</f>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="H20" s="11">
+        <v>11.31</v>
+      </c>
+      <c r="I20" s="6">
+        <v>600</v>
+      </c>
+      <c r="J20" s="6">
+        <v>1700</v>
+      </c>
+      <c r="K20" s="11">
+        <f>LN(J20/I20)</f>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="L20" s="6">
+        <f>(F20/(G20*H20))*K20</f>
+        <v>6.5834788077571135E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="6">
+        <v>200</v>
+      </c>
+      <c r="C21" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="D21" s="6">
+        <f>B21*C21</f>
+        <v>500</v>
+      </c>
+      <c r="E21" s="6">
+        <v>64</v>
+      </c>
+      <c r="F21" s="11">
+        <f t="shared" ref="F21:F27" si="0">D21/E21</f>
+        <v>7.8125</v>
+      </c>
+      <c r="G21" s="11">
+        <f t="shared" ref="G21:G27" si="1">4*PI()</f>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="H21" s="11">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="I21" s="6">
+        <v>600</v>
+      </c>
+      <c r="J21" s="6">
+        <v>1700</v>
+      </c>
+      <c r="K21" s="11">
+        <f t="shared" ref="K21:K27" si="2">LN(J21/I21)</f>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="L21" s="6">
+        <f t="shared" ref="L21:L27" si="3">(F21/(G21*H21))*K21</f>
+        <v>7.5727582319586012E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="6">
+        <v>170</v>
+      </c>
+      <c r="C22" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="D22" s="6">
+        <f t="shared" ref="D22:D27" si="4">B22*C22</f>
+        <v>425</v>
+      </c>
+      <c r="E22" s="6">
+        <v>64</v>
+      </c>
+      <c r="F22" s="11">
+        <f t="shared" si="0"/>
+        <v>6.640625</v>
+      </c>
+      <c r="G22" s="11">
+        <f t="shared" si="1"/>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="H22" s="11">
+        <v>6.18</v>
+      </c>
+      <c r="I22" s="6">
+        <v>600</v>
+      </c>
+      <c r="J22" s="6">
+        <v>1700</v>
+      </c>
+      <c r="K22" s="11">
+        <f t="shared" si="2"/>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="L22" s="6">
+        <f t="shared" si="3"/>
+        <v>8.9053431150095702E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="6">
+        <v>140</v>
+      </c>
+      <c r="C23" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="D23" s="6">
+        <f t="shared" si="4"/>
+        <v>350</v>
+      </c>
+      <c r="E23" s="6">
+        <v>64</v>
+      </c>
+      <c r="F23" s="11">
+        <f t="shared" si="0"/>
+        <v>5.46875</v>
+      </c>
+      <c r="G23" s="11">
+        <f t="shared" si="1"/>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="H23" s="11">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="I23" s="6">
+        <v>600</v>
+      </c>
+      <c r="J23" s="6">
+        <v>1700</v>
+      </c>
+      <c r="K23" s="11">
+        <f t="shared" si="2"/>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="L23" s="6">
+        <f t="shared" si="3"/>
+        <v>0.10816935087893134</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="6">
+        <v>110</v>
+      </c>
+      <c r="C24" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="D24" s="6">
+        <f t="shared" si="4"/>
+        <v>275</v>
+      </c>
+      <c r="E24" s="6">
+        <v>64</v>
+      </c>
+      <c r="F24" s="11">
+        <f t="shared" si="0"/>
+        <v>4.296875</v>
+      </c>
+      <c r="G24" s="11">
+        <f t="shared" si="1"/>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="H24" s="11">
+        <v>2.59</v>
+      </c>
+      <c r="I24" s="6">
+        <v>600</v>
+      </c>
+      <c r="J24" s="6">
+        <v>1700</v>
+      </c>
+      <c r="K24" s="11">
+        <f t="shared" si="2"/>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="L24" s="6">
+        <f t="shared" si="3"/>
+        <v>0.1374938053505225</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="6">
+        <v>80</v>
+      </c>
+      <c r="C25" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="D25" s="6">
+        <f t="shared" si="4"/>
+        <v>200</v>
+      </c>
+      <c r="E25" s="6">
+        <v>64</v>
+      </c>
+      <c r="F25" s="11">
+        <f t="shared" si="0"/>
+        <v>3.125</v>
+      </c>
+      <c r="G25" s="11">
+        <f t="shared" si="1"/>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="H25" s="11">
+        <v>1.37</v>
+      </c>
+      <c r="I25" s="6">
+        <v>600</v>
+      </c>
+      <c r="J25" s="6">
+        <v>1700</v>
+      </c>
+      <c r="K25" s="11">
+        <f t="shared" si="2"/>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="L25" s="6">
+        <f t="shared" si="3"/>
+        <v>0.18904257776130232</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="6">
+        <v>50</v>
+      </c>
+      <c r="C26" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="D26" s="6">
+        <f t="shared" si="4"/>
+        <v>125</v>
+      </c>
+      <c r="E26" s="6">
+        <v>64</v>
+      </c>
+      <c r="F26" s="11">
+        <f t="shared" si="0"/>
+        <v>1.953125</v>
+      </c>
+      <c r="G26" s="11">
+        <f t="shared" si="1"/>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="H26" s="11">
+        <v>0.53</v>
+      </c>
+      <c r="I26" s="6">
+        <v>600</v>
+      </c>
+      <c r="J26" s="6">
+        <v>1700</v>
+      </c>
+      <c r="K26" s="11">
+        <f t="shared" si="2"/>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="L26" s="6">
+        <f t="shared" si="3"/>
+        <v>0.30541076831719832</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="6">
+        <v>20</v>
+      </c>
+      <c r="C27" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="D27" s="6">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="E27" s="6">
+        <v>64</v>
+      </c>
+      <c r="F27" s="11">
+        <f t="shared" si="0"/>
+        <v>0.78125</v>
+      </c>
+      <c r="G27" s="11">
+        <f t="shared" si="1"/>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="H27" s="11">
+        <v>0.09</v>
+      </c>
+      <c r="I27" s="6">
+        <v>600</v>
+      </c>
+      <c r="J27" s="6">
+        <v>1700</v>
+      </c>
+      <c r="K27" s="11">
+        <f t="shared" si="2"/>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="L27" s="6">
+        <f t="shared" si="3"/>
+        <v>0.71941203203606718</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K31" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="4">
+        <f>B20*C20</f>
+        <v>575</v>
+      </c>
+      <c r="C33" s="4">
+        <v>1.47</v>
+      </c>
+      <c r="D33" s="7">
+        <v>32</v>
+      </c>
+      <c r="E33" s="7">
+        <f>Table13[[#This Row],[R'' ]]*Table13[[#This Row],[L_heat]]</f>
+        <v>47.04</v>
+      </c>
+      <c r="F33" s="8">
+        <f>Table13[[#This Row],[voltage]]^2/(Table13[[#This Row],[R]]*Table13[[#This Row],[L_heat]])</f>
+        <v>219.64352147108843</v>
+      </c>
+      <c r="G33" s="8">
+        <f>4*PI()</f>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="H33" s="8">
+        <v>11.31</v>
+      </c>
+      <c r="I33" s="4">
+        <v>600</v>
+      </c>
+      <c r="J33" s="4">
+        <v>1700</v>
+      </c>
+      <c r="K33" s="8">
+        <f>LN(J33/I33)</f>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="L33" s="6">
+        <f>(F33/(G33*H33))*K33</f>
+        <v>1.609481426216131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="4">
+        <f t="shared" ref="B34:B40" si="5">B21*C21</f>
+        <v>500</v>
+      </c>
+      <c r="C34" s="4">
+        <v>1.47</v>
+      </c>
+      <c r="D34" s="7">
+        <v>32</v>
+      </c>
+      <c r="E34" s="7">
+        <f>Table13[[#This Row],[R'' ]]*Table13[[#This Row],[L_heat]]</f>
+        <v>47.04</v>
+      </c>
+      <c r="F34" s="8">
+        <f>Table13[[#This Row],[voltage]]^2/(Table13[[#This Row],[R]]*Table13[[#This Row],[L_heat]])</f>
+        <v>166.08205782312925</v>
+      </c>
+      <c r="G34" s="8">
+        <f t="shared" ref="G34:G40" si="6">4*PI()</f>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="H34" s="8">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="I34" s="4">
+        <v>600</v>
+      </c>
+      <c r="J34" s="4">
+        <v>1700</v>
+      </c>
+      <c r="K34" s="8">
+        <f t="shared" ref="K34:K40" si="7">LN(J34/I34)</f>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="L34" s="6">
+        <f t="shared" ref="L34:L40" si="8">(F34/(G34*H34))*K34</f>
+        <v>1.60985506631773</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="4">
+        <f t="shared" si="5"/>
+        <v>425</v>
+      </c>
+      <c r="C35" s="4">
+        <v>1.47</v>
+      </c>
+      <c r="D35" s="7">
+        <v>32</v>
+      </c>
+      <c r="E35" s="7">
+        <f>Table13[[#This Row],[R'' ]]*Table13[[#This Row],[L_heat]]</f>
+        <v>47.04</v>
+      </c>
+      <c r="F35" s="8">
+        <f>Table13[[#This Row],[voltage]]^2/(Table13[[#This Row],[R]]*Table13[[#This Row],[L_heat]])</f>
+        <v>119.99428677721089</v>
+      </c>
+      <c r="G35" s="8">
+        <f t="shared" si="6"/>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="H35" s="8">
+        <v>6.18</v>
+      </c>
+      <c r="I35" s="4">
+        <v>600</v>
+      </c>
+      <c r="J35" s="4">
+        <v>1700</v>
+      </c>
+      <c r="K35" s="8">
+        <f t="shared" si="7"/>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="L35" s="6">
+        <f t="shared" si="8"/>
+        <v>1.6091712686560662</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="4">
+        <f t="shared" si="5"/>
+        <v>350</v>
+      </c>
+      <c r="C36" s="4">
+        <v>1.47</v>
+      </c>
+      <c r="D36" s="7">
+        <v>32</v>
+      </c>
+      <c r="E36" s="7">
+        <f>Table13[[#This Row],[R'' ]]*Table13[[#This Row],[L_heat]]</f>
+        <v>47.04</v>
+      </c>
+      <c r="F36" s="8">
+        <f>Table13[[#This Row],[voltage]]^2/(Table13[[#This Row],[R]]*Table13[[#This Row],[L_heat]])</f>
+        <v>81.380208333333329</v>
+      </c>
+      <c r="G36" s="8">
+        <f t="shared" si="6"/>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="H36" s="8">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="I36" s="4">
+        <v>600</v>
+      </c>
+      <c r="J36" s="4">
+        <v>1700</v>
+      </c>
+      <c r="K36" s="8">
+        <f t="shared" si="7"/>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="L36" s="6">
+        <f t="shared" si="8"/>
+        <v>1.6096629595079068</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="4">
+        <f t="shared" si="5"/>
+        <v>275</v>
+      </c>
+      <c r="C37" s="4">
+        <v>1.47</v>
+      </c>
+      <c r="D37" s="7">
+        <v>32</v>
+      </c>
+      <c r="E37" s="7">
+        <f>Table13[[#This Row],[R'' ]]*Table13[[#This Row],[L_heat]]</f>
+        <v>47.04</v>
+      </c>
+      <c r="F37" s="8">
+        <f>Table13[[#This Row],[voltage]]^2/(Table13[[#This Row],[R]]*Table13[[#This Row],[L_heat]])</f>
+        <v>50.239822491496597</v>
+      </c>
+      <c r="G37" s="8">
+        <f t="shared" si="6"/>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="H37" s="8">
+        <v>2.59</v>
+      </c>
+      <c r="I37" s="4">
+        <v>600</v>
+      </c>
+      <c r="J37" s="4">
+        <v>1700</v>
+      </c>
+      <c r="K37" s="8">
+        <f t="shared" si="7"/>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="L37" s="6">
+        <f t="shared" si="8"/>
+        <v>1.6076018907905478</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="4">
+        <f t="shared" si="5"/>
+        <v>200</v>
+      </c>
+      <c r="C38" s="4">
+        <v>1.47</v>
+      </c>
+      <c r="D38" s="7">
+        <v>32</v>
+      </c>
+      <c r="E38" s="7">
+        <f>Table13[[#This Row],[R'' ]]*Table13[[#This Row],[L_heat]]</f>
+        <v>47.04</v>
+      </c>
+      <c r="F38" s="8">
+        <f>Table13[[#This Row],[voltage]]^2/(Table13[[#This Row],[R]]*Table13[[#This Row],[L_heat]])</f>
+        <v>26.573129251700681</v>
+      </c>
+      <c r="G38" s="8">
+        <f t="shared" si="6"/>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="H38" s="8">
+        <v>1.37</v>
+      </c>
+      <c r="I38" s="4">
+        <v>600</v>
+      </c>
+      <c r="J38" s="4">
+        <v>1700</v>
+      </c>
+      <c r="K38" s="8">
+        <f t="shared" si="7"/>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="L38" s="6">
+        <f t="shared" si="8"/>
+        <v>1.6075049129362444</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="4">
+        <f t="shared" si="5"/>
+        <v>125</v>
+      </c>
+      <c r="C39" s="4">
+        <v>1.47</v>
+      </c>
+      <c r="D39" s="7">
+        <v>32</v>
+      </c>
+      <c r="E39" s="7">
+        <f>Table13[[#This Row],[R'' ]]*Table13[[#This Row],[L_heat]]</f>
+        <v>47.04</v>
+      </c>
+      <c r="F39" s="8">
+        <f>Table13[[#This Row],[voltage]]^2/(Table13[[#This Row],[R]]*Table13[[#This Row],[L_heat]])</f>
+        <v>10.380128613945578</v>
+      </c>
+      <c r="G39" s="8">
+        <f t="shared" si="6"/>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="H39" s="8">
+        <v>0.53</v>
+      </c>
+      <c r="I39" s="4">
+        <v>600</v>
+      </c>
+      <c r="J39" s="4">
+        <v>1700</v>
+      </c>
+      <c r="K39" s="8">
+        <f t="shared" si="7"/>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="L39" s="6">
+        <f t="shared" si="8"/>
+        <v>1.6231439642708243</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="4">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="C40" s="4">
+        <v>1.47</v>
+      </c>
+      <c r="D40" s="7">
+        <v>32</v>
+      </c>
+      <c r="E40" s="7">
+        <f>Table13[[#This Row],[R'' ]]*Table13[[#This Row],[L_heat]]</f>
+        <v>47.04</v>
+      </c>
+      <c r="F40" s="8">
+        <f>Table13[[#This Row],[voltage]]^2/(Table13[[#This Row],[R]]*Table13[[#This Row],[L_heat]])</f>
+        <v>1.6608205782312926</v>
+      </c>
+      <c r="G40" s="8">
+        <f t="shared" si="6"/>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="H40" s="8">
+        <v>0.09</v>
+      </c>
+      <c r="I40" s="4">
+        <v>600</v>
+      </c>
+      <c r="J40" s="4">
+        <v>1700</v>
+      </c>
+      <c r="K40" s="8">
+        <f t="shared" si="7"/>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="L40" s="6">
+        <f t="shared" si="8"/>
+        <v>1.5293623130018437</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <tableParts count="2">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/modelling/wsf grondwaterstroming/Properties_calculator.xlsx
+++ b/modelling/wsf grondwaterstroming/Properties_calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Gitclones\FusionFiber\modelling\wsf grondwaterstroming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92816463-BEF9-420C-8C5F-230CC172BC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2588B3D0-34A3-45A9-A87C-5AA277EEC78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{3632657A-28F7-4C1C-ABB4-32E130E65C30}"/>
   </bookViews>

--- a/modelling/wsf grondwaterstroming/Properties_calculator.xlsx
+++ b/modelling/wsf grondwaterstroming/Properties_calculator.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Gitclones\FusionFiber\modelling\wsf grondwaterstroming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2588B3D0-34A3-45A9-A87C-5AA277EEC78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C73F58B-E895-430C-9518-F46736A27C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{3632657A-28F7-4C1C-ABB4-32E130E65C30}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="71">
   <si>
     <t>n</t>
   </si>
@@ -213,6 +213,42 @@
   </si>
   <si>
     <t>Rtotal</t>
+  </si>
+  <si>
+    <t>gw300</t>
+  </si>
+  <si>
+    <t>Expected conductivty</t>
+  </si>
+  <si>
+    <t>gw301</t>
+  </si>
+  <si>
+    <t>gw302</t>
+  </si>
+  <si>
+    <t>gw303</t>
+  </si>
+  <si>
+    <t>gw304</t>
+  </si>
+  <si>
+    <t>gw305</t>
+  </si>
+  <si>
+    <t>gw306</t>
+  </si>
+  <si>
+    <t>gw307</t>
+  </si>
+  <si>
+    <t>gw308</t>
+  </si>
+  <si>
+    <t>gw309</t>
+  </si>
+  <si>
+    <t>gw310</t>
   </si>
 </sst>
 </file>
@@ -275,23 +311,27 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -299,11 +339,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4"/>
+      </right>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -333,17 +419,59 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="16">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -356,16 +484,13 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color theme="4"/>
+        <color auto="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <numFmt numFmtId="164" formatCode="0.000"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -462,6 +587,26 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -607,13 +752,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>164124</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>169984</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>572059</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>8186</xdr:rowOff>
@@ -659,14 +804,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>785447</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>169982</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>781722</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>575982</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>167554</xdr:rowOff>
     </xdr:to>
@@ -710,18 +855,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{61B2F13E-E38A-4556-AD9E-4A31FC65E5B2}" name="Table134" displayName="Table134" ref="A17:O26" totalsRowShown="0" headerRowDxfId="14">
-  <autoFilter ref="A17:O26" xr:uid="{61B2F13E-E38A-4556-AD9E-4A31FC65E5B2}"/>
-  <tableColumns count="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{61B2F13E-E38A-4556-AD9E-4A31FC65E5B2}" name="Table134" displayName="Table134" ref="A17:P27" totalsRowShown="0" headerRowDxfId="15">
+  <autoFilter ref="A17:P27" xr:uid="{61B2F13E-E38A-4556-AD9E-4A31FC65E5B2}"/>
+  <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{D88FD9F6-4197-4562-AEB5-6E64BB7B60DF}" name="test_id"/>
-    <tableColumn id="2" xr3:uid="{60857CD5-5FC9-4195-B59E-DCF7E4200979}" name="voltage" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{DC49E5D0-E51E-4B30-8721-2B94794996C4}" name="R' " dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{D3B11A5D-6B20-4BAD-9548-D20A742D41CD}" name="L_heat" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{4584E915-A1FB-40E2-8D9A-AF0AA3924EB8}" name="Rtotal" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{824832D0-1465-46BF-B1DB-BC3BB2B60BB1}" name="Q" dataDxfId="9">
+    <tableColumn id="2" xr3:uid="{60857CD5-5FC9-4195-B59E-DCF7E4200979}" name="voltage" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{DC49E5D0-E51E-4B30-8721-2B94794996C4}" name="R' " dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{D3B11A5D-6B20-4BAD-9548-D20A742D41CD}" name="L_heat" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{4584E915-A1FB-40E2-8D9A-AF0AA3924EB8}" name="Rtotal" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{824832D0-1465-46BF-B1DB-BC3BB2B60BB1}" name="Q" dataDxfId="10">
       <calculatedColumnFormula>#REF!/D18</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{EA6FF7B3-D4B1-4528-B1DE-055780E0D12E}" name="ncores" dataDxfId="0"/>
+    <tableColumn id="15" xr3:uid="{EA6FF7B3-D4B1-4528-B1DE-055780E0D12E}" name="ncores" dataDxfId="9"/>
     <tableColumn id="13" xr3:uid="{948E3691-0FA0-4A22-9288-16019CC9AC13}" name="Qtotal" dataDxfId="8"/>
     <tableColumn id="7" xr3:uid="{0EDD676B-B419-4ABD-9D3B-FA77118332A8}" name="4pi" dataDxfId="7">
       <calculatedColumnFormula>4*PI()</calculatedColumnFormula>
@@ -735,7 +880,8 @@
     <tableColumn id="12" xr3:uid="{592CBC98-0598-4037-9EBB-0C85EDD981BD}" name="themal conductivity" dataDxfId="2">
       <calculatedColumnFormula>(F18/(I18*J18))*M18</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{5268CFBE-FCA9-49F7-84B9-D28633D99E4F}" name="Relative error" dataDxfId="1">
+    <tableColumn id="16" xr3:uid="{B3214748-DDC5-499A-9049-D295CF923A61}" name="Expected conductivty" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{5268CFBE-FCA9-49F7-84B9-D28633D99E4F}" name="Relative error" dataDxfId="0">
       <calculatedColumnFormula>100*((Table134[[#This Row],[themal conductivity]]/1.6)-1)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1060,7 +1206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE086DA3-B7D9-4EBD-B1A4-5E6F632602CC}">
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="11" max="11" width="9.77734375" customWidth="1"/>
@@ -1241,7 +1387,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>42</v>
       </c>
@@ -1284,11 +1430,14 @@
       <c r="N17" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="O17" s="2" t="s">
+      <c r="O17" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="P17" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>3</v>
       </c>
@@ -1331,12 +1480,15 @@
       <c r="N18" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="O18" t="s">
+      <c r="O18" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="P18" t="s">
         <v>55</v>
       </c>
-      <c r="P18"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q18"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -1369,7 +1521,7 @@
         <v>12.566370614359172</v>
       </c>
       <c r="J19" s="14">
-        <v>1.81</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="K19" s="3">
         <v>600</v>
@@ -1383,14 +1535,17 @@
       </c>
       <c r="N19" s="11">
         <f>(H19/(I19*J19))*M19</f>
-        <v>4.2034305037403428</v>
-      </c>
-      <c r="O19" s="12">
+        <v>1.6085008904376361</v>
+      </c>
+      <c r="O19" s="11">
+        <v>1.6</v>
+      </c>
+      <c r="P19" s="12">
         <f>100*((Table134[[#This Row],[themal conductivity]]/1.6)-1)</f>
-        <v>162.71440648377143</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.53130565235224303</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -1423,7 +1578,7 @@
         <v>12.566370614359172</v>
       </c>
       <c r="J20" s="14">
-        <v>1.37</v>
+        <v>3.58</v>
       </c>
       <c r="K20" s="3">
         <v>600</v>
@@ -1437,14 +1592,17 @@
       </c>
       <c r="N20" s="11">
         <f t="shared" ref="N20:N26" si="2">(H20/(I20*J20))*M20</f>
-        <v>4.199196507262025</v>
-      </c>
-      <c r="O20" s="12">
+        <v>1.606955087974574</v>
+      </c>
+      <c r="O20" s="11">
+        <v>1.6</v>
+      </c>
+      <c r="P20" s="12">
         <f>100*((Table134[[#This Row],[themal conductivity]]/1.6)-1)</f>
-        <v>162.44978170387654</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.43469299841085718</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>31</v>
       </c>
@@ -1477,7 +1635,7 @@
         <v>12.566370614359172</v>
       </c>
       <c r="J21" s="14">
-        <v>0.99</v>
+        <v>2.58</v>
       </c>
       <c r="K21" s="3">
         <v>600</v>
@@ -1491,14 +1649,17 @@
       </c>
       <c r="N21" s="11">
         <f t="shared" si="2"/>
-        <v>4.1984542250511456</v>
-      </c>
-      <c r="O21" s="12">
+        <v>1.6110347607754398</v>
+      </c>
+      <c r="O21" s="11">
+        <v>1.6</v>
+      </c>
+      <c r="P21" s="12">
         <f>100*((Table134[[#This Row],[themal conductivity]]/1.6)-1)</f>
-        <v>162.40338906569659</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.68967254846499237</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>32</v>
       </c>
@@ -1531,7 +1692,7 @@
         <v>12.566370614359172</v>
       </c>
       <c r="J22" s="14">
-        <v>0.67</v>
+        <v>1.75</v>
       </c>
       <c r="K22" s="3">
         <v>600</v>
@@ -1545,14 +1706,17 @@
       </c>
       <c r="N22" s="11">
         <f t="shared" si="2"/>
-        <v>4.2073442019776088</v>
-      </c>
-      <c r="O22" s="12">
+        <v>1.6108117801857129</v>
+      </c>
+      <c r="O22" s="11">
+        <v>1.6</v>
+      </c>
+      <c r="P22" s="12">
         <f>100*((Table134[[#This Row],[themal conductivity]]/1.6)-1)</f>
-        <v>162.95901262360056</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.67573626160704059</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -1585,7 +1749,7 @@
         <v>12.566370614359172</v>
       </c>
       <c r="J23" s="14">
-        <v>0.41</v>
+        <v>1.08</v>
       </c>
       <c r="K23" s="3">
         <v>600</v>
@@ -1599,14 +1763,17 @@
       </c>
       <c r="N23" s="11">
         <f t="shared" si="2"/>
-        <v>4.2445171037123544</v>
-      </c>
-      <c r="O23" s="12">
+        <v>1.6113444560389489</v>
+      </c>
+      <c r="O23" s="11">
+        <v>1.6</v>
+      </c>
+      <c r="P23" s="12">
         <f>100*((Table134[[#This Row],[themal conductivity]]/1.6)-1)</f>
-        <v>165.28231898202216</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.70902850243430571</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -1639,7 +1806,7 @@
         <v>12.566370614359172</v>
       </c>
       <c r="J24" s="14">
-        <v>0.22</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="K24" s="3">
         <v>600</v>
@@ -1653,14 +1820,17 @@
       </c>
       <c r="N24" s="11">
         <f t="shared" si="2"/>
-        <v>4.1839267017810737</v>
-      </c>
-      <c r="O24" s="12">
+        <v>1.614848902441818</v>
+      </c>
+      <c r="O24" s="11">
+        <v>1.6</v>
+      </c>
+      <c r="P24" s="12">
         <f>100*((Table134[[#This Row],[themal conductivity]]/1.6)-1)</f>
-        <v>161.49541886131709</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.92805640261361955</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>35</v>
       </c>
@@ -1693,7 +1863,7 @@
         <v>12.566370614359172</v>
       </c>
       <c r="J25" s="14">
-        <v>0.09</v>
+        <v>0.22</v>
       </c>
       <c r="K25" s="3">
         <v>600</v>
@@ -1707,14 +1877,17 @@
       </c>
       <c r="N25" s="11">
         <f t="shared" si="2"/>
-        <v>3.9950688992701218</v>
-      </c>
-      <c r="O25" s="12">
+        <v>1.634346367883232</v>
+      </c>
+      <c r="O25" s="11">
+        <v>1.6</v>
+      </c>
+      <c r="P25" s="12">
         <f>100*((Table134[[#This Row],[themal conductivity]]/1.6)-1)</f>
-        <v>149.6918062043826</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+        <v>2.1466479927019888</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>36</v>
       </c>
@@ -1747,7 +1920,7 @@
         <v>12.566370614359172</v>
       </c>
       <c r="J26" s="14">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="K26" s="3">
         <v>600</v>
@@ -1761,14 +1934,797 @@
       </c>
       <c r="N26" s="11">
         <f t="shared" si="2"/>
-        <v>5.7528992149489753</v>
-      </c>
-      <c r="O26" s="12">
+        <v>1.4382248037372438</v>
+      </c>
+      <c r="O26" s="11">
+        <v>1.6</v>
+      </c>
+      <c r="P26" s="12">
         <f>100*((Table134[[#This Row],[themal conductivity]]/1.6)-1)</f>
-        <v>259.55620093431094</v>
+        <v>-10.110949766422262</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="15"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="2"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A29" s="1"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A30" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G30" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="H30" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="I30" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="J30" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="K30" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="L30" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="M30" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="O30" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="P30" s="18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A31" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="H31" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="I31" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="K31" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L31" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M31" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="N31" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="O31" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="P31" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A32" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" s="20">
+        <v>230</v>
+      </c>
+      <c r="C32" s="20">
+        <v>1.47</v>
+      </c>
+      <c r="D32" s="21">
+        <v>28</v>
+      </c>
+      <c r="E32" s="21">
+        <f>C32*D32</f>
+        <v>41.16</v>
+      </c>
+      <c r="F32" s="24">
+        <f>B32^2/(E32*D32)</f>
+        <v>45.901013466611133</v>
+      </c>
+      <c r="G32" s="25">
+        <v>2</v>
+      </c>
+      <c r="H32" s="24">
+        <f>F32*G32</f>
+        <v>91.802026933222265</v>
+      </c>
+      <c r="I32" s="24">
+        <f>4*PI()</f>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="J32" s="26">
+        <v>7.39</v>
+      </c>
+      <c r="K32" s="20">
+        <v>600</v>
+      </c>
+      <c r="L32" s="20">
+        <v>1700</v>
+      </c>
+      <c r="M32" s="27">
+        <f>LN(L32/K32)</f>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="N32" s="28">
+        <f>(H32/(I32*J32))*M32</f>
+        <v>1.029527633527743</v>
+      </c>
+      <c r="O32" s="28">
+        <v>1</v>
+      </c>
+      <c r="P32" s="29">
+        <f>100*((N32/O32)-1)</f>
+        <v>2.9527633527743014</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A33" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" s="20">
+        <v>230</v>
+      </c>
+      <c r="C33" s="20">
+        <v>1.47</v>
+      </c>
+      <c r="D33" s="21">
+        <v>28</v>
+      </c>
+      <c r="E33" s="21">
+        <f t="shared" ref="E33:E42" si="3">C33*D33</f>
+        <v>41.16</v>
+      </c>
+      <c r="F33" s="24">
+        <f t="shared" ref="F33:F42" si="4">B33^2/(E33*D33)</f>
+        <v>45.901013466611133</v>
+      </c>
+      <c r="G33" s="25">
+        <v>2</v>
+      </c>
+      <c r="H33" s="24">
+        <f t="shared" ref="H33:H42" si="5">F33*G33</f>
+        <v>91.802026933222265</v>
+      </c>
+      <c r="I33" s="24">
+        <f t="shared" ref="I33:I42" si="6">4*PI()</f>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="J33" s="26">
+        <v>6.22</v>
+      </c>
+      <c r="K33" s="20">
+        <v>600</v>
+      </c>
+      <c r="L33" s="20">
+        <v>1700</v>
+      </c>
+      <c r="M33" s="27">
+        <f t="shared" ref="M33:M39" si="7">LN(L33/K33)</f>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="N33" s="28">
+        <f t="shared" ref="N33:N42" si="8">(H33/(I33*J33))*M33</f>
+        <v>1.2231847607347299</v>
+      </c>
+      <c r="O33" s="28">
+        <v>1.2</v>
+      </c>
+      <c r="P33" s="29">
+        <f t="shared" ref="P33:P42" si="9">100*((N33/O33)-1)</f>
+        <v>1.9320633945608234</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A34" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="20">
+        <v>230</v>
+      </c>
+      <c r="C34" s="20">
+        <v>1.47</v>
+      </c>
+      <c r="D34" s="21">
+        <v>28</v>
+      </c>
+      <c r="E34" s="21">
+        <f t="shared" si="3"/>
+        <v>41.16</v>
+      </c>
+      <c r="F34" s="24">
+        <f t="shared" si="4"/>
+        <v>45.901013466611133</v>
+      </c>
+      <c r="G34" s="25">
+        <v>2</v>
+      </c>
+      <c r="H34" s="24">
+        <f t="shared" si="5"/>
+        <v>91.802026933222265</v>
+      </c>
+      <c r="I34" s="24">
+        <f t="shared" si="6"/>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="J34" s="26">
+        <v>5.37</v>
+      </c>
+      <c r="K34" s="20">
+        <v>600</v>
+      </c>
+      <c r="L34" s="20">
+        <v>1700</v>
+      </c>
+      <c r="M34" s="27">
+        <f t="shared" si="7"/>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="N34" s="28">
+        <f t="shared" si="8"/>
+        <v>1.4167987358975831</v>
+      </c>
+      <c r="O34" s="28">
+        <v>1.4</v>
+      </c>
+      <c r="P34" s="29">
+        <f t="shared" si="9"/>
+        <v>1.1999097069702369</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A35" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" s="20">
+        <v>230</v>
+      </c>
+      <c r="C35" s="20">
+        <v>1.47</v>
+      </c>
+      <c r="D35" s="21">
+        <v>28</v>
+      </c>
+      <c r="E35" s="21">
+        <f t="shared" si="3"/>
+        <v>41.16</v>
+      </c>
+      <c r="F35" s="24">
+        <f t="shared" si="4"/>
+        <v>45.901013466611133</v>
+      </c>
+      <c r="G35" s="25">
+        <v>2</v>
+      </c>
+      <c r="H35" s="24">
+        <f t="shared" si="5"/>
+        <v>91.802026933222265</v>
+      </c>
+      <c r="I35" s="24">
+        <f t="shared" si="6"/>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="J35" s="26">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="K35" s="20">
+        <v>600</v>
+      </c>
+      <c r="L35" s="20">
+        <v>1700</v>
+      </c>
+      <c r="M35" s="27">
+        <f t="shared" si="7"/>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="N35" s="28">
+        <f t="shared" si="8"/>
+        <v>1.6085008904376361</v>
+      </c>
+      <c r="O35" s="28">
+        <v>1.6</v>
+      </c>
+      <c r="P35" s="29">
+        <f t="shared" si="9"/>
+        <v>0.53130565235224303</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A36" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B36" s="20">
+        <v>230</v>
+      </c>
+      <c r="C36" s="20">
+        <v>1.47</v>
+      </c>
+      <c r="D36" s="21">
+        <v>28</v>
+      </c>
+      <c r="E36" s="21">
+        <f t="shared" si="3"/>
+        <v>41.16</v>
+      </c>
+      <c r="F36" s="24">
+        <f t="shared" si="4"/>
+        <v>45.901013466611133</v>
+      </c>
+      <c r="G36" s="25">
+        <v>2</v>
+      </c>
+      <c r="H36" s="24">
+        <f t="shared" si="5"/>
+        <v>91.802026933222265</v>
+      </c>
+      <c r="I36" s="24">
+        <f t="shared" si="6"/>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="J36" s="26">
+        <v>4.22</v>
+      </c>
+      <c r="K36" s="20">
+        <v>600</v>
+      </c>
+      <c r="L36" s="20">
+        <v>1700</v>
+      </c>
+      <c r="M36" s="27">
+        <f t="shared" si="7"/>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="N36" s="28">
+        <f t="shared" si="8"/>
+        <v>1.8028931781445545</v>
+      </c>
+      <c r="O36" s="28">
+        <v>1.8</v>
+      </c>
+      <c r="P36" s="29">
+        <f t="shared" si="9"/>
+        <v>0.16073211914191532</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A37" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="B37" s="20">
+        <v>230</v>
+      </c>
+      <c r="C37" s="20">
+        <v>1.47</v>
+      </c>
+      <c r="D37" s="21">
+        <v>28</v>
+      </c>
+      <c r="E37" s="21">
+        <f t="shared" si="3"/>
+        <v>41.16</v>
+      </c>
+      <c r="F37" s="24">
+        <f t="shared" si="4"/>
+        <v>45.901013466611133</v>
+      </c>
+      <c r="G37" s="25">
+        <v>2</v>
+      </c>
+      <c r="H37" s="24">
+        <f t="shared" si="5"/>
+        <v>91.802026933222265</v>
+      </c>
+      <c r="I37" s="24">
+        <f t="shared" si="6"/>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="J37" s="26">
+        <v>3.81</v>
+      </c>
+      <c r="K37" s="20">
+        <v>600</v>
+      </c>
+      <c r="L37" s="20">
+        <v>1700</v>
+      </c>
+      <c r="M37" s="27">
+        <f t="shared" si="7"/>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="N37" s="28">
+        <f t="shared" si="8"/>
+        <v>1.9969053049265144</v>
+      </c>
+      <c r="O37" s="28">
+        <v>2</v>
+      </c>
+      <c r="P37" s="29">
+        <f t="shared" si="9"/>
+        <v>-0.15473475367427936</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A38" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B38" s="20">
+        <v>230</v>
+      </c>
+      <c r="C38" s="20">
+        <v>1.47</v>
+      </c>
+      <c r="D38" s="21">
+        <v>28</v>
+      </c>
+      <c r="E38" s="21">
+        <f t="shared" si="3"/>
+        <v>41.16</v>
+      </c>
+      <c r="F38" s="24">
+        <f t="shared" si="4"/>
+        <v>45.901013466611133</v>
+      </c>
+      <c r="G38" s="25">
+        <v>2</v>
+      </c>
+      <c r="H38" s="24">
+        <f t="shared" si="5"/>
+        <v>91.802026933222265</v>
+      </c>
+      <c r="I38" s="24">
+        <f t="shared" si="6"/>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="J38" s="26">
+        <v>3.48</v>
+      </c>
+      <c r="K38" s="20">
+        <v>600</v>
+      </c>
+      <c r="L38" s="20">
+        <v>1700</v>
+      </c>
+      <c r="M38" s="27">
+        <f t="shared" si="7"/>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="N38" s="28">
+        <f t="shared" si="8"/>
+        <v>2.1862670148764427</v>
+      </c>
+      <c r="O38" s="28">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="P38" s="29">
+        <f t="shared" si="9"/>
+        <v>-0.62422659652533463</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A39" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="B39" s="20">
+        <v>230</v>
+      </c>
+      <c r="C39" s="20">
+        <v>1.47</v>
+      </c>
+      <c r="D39" s="21">
+        <v>28</v>
+      </c>
+      <c r="E39" s="21">
+        <f t="shared" si="3"/>
+        <v>41.16</v>
+      </c>
+      <c r="F39" s="24">
+        <f t="shared" si="4"/>
+        <v>45.901013466611133</v>
+      </c>
+      <c r="G39" s="25">
+        <v>2</v>
+      </c>
+      <c r="H39" s="24">
+        <f t="shared" si="5"/>
+        <v>91.802026933222265</v>
+      </c>
+      <c r="I39" s="24">
+        <f t="shared" si="6"/>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="J39" s="26">
+        <v>3.2</v>
+      </c>
+      <c r="K39" s="20">
+        <v>600</v>
+      </c>
+      <c r="L39" s="20">
+        <v>1700</v>
+      </c>
+      <c r="M39" s="27">
+        <f t="shared" si="7"/>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="N39" s="28">
+        <f t="shared" si="8"/>
+        <v>2.3775653786781317</v>
+      </c>
+      <c r="O39" s="28">
+        <v>2.4</v>
+      </c>
+      <c r="P39" s="29">
+        <f t="shared" si="9"/>
+        <v>-0.93477588841117676</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A40" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="B40" s="20">
+        <v>230</v>
+      </c>
+      <c r="C40" s="20">
+        <v>1.47</v>
+      </c>
+      <c r="D40" s="21">
+        <v>28</v>
+      </c>
+      <c r="E40" s="21">
+        <f t="shared" si="3"/>
+        <v>41.16</v>
+      </c>
+      <c r="F40" s="24">
+        <f t="shared" si="4"/>
+        <v>45.901013466611133</v>
+      </c>
+      <c r="G40" s="25">
+        <v>2</v>
+      </c>
+      <c r="H40" s="24">
+        <f t="shared" si="5"/>
+        <v>91.802026933222265</v>
+      </c>
+      <c r="I40" s="24">
+        <f t="shared" si="6"/>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="J40" s="30">
+        <v>2.96</v>
+      </c>
+      <c r="K40" s="20">
+        <v>600</v>
+      </c>
+      <c r="L40" s="20">
+        <v>1700</v>
+      </c>
+      <c r="M40" s="27">
+        <f t="shared" ref="M40:M42" si="10">LN(L40/K40)</f>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="N40" s="28">
+        <f t="shared" si="8"/>
+        <v>2.5703409499223042</v>
+      </c>
+      <c r="O40" s="31">
+        <v>2.6</v>
+      </c>
+      <c r="P40" s="29">
+        <f t="shared" si="9"/>
+        <v>-1.1407326952959984</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A41" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41" s="20">
+        <v>230</v>
+      </c>
+      <c r="C41" s="20">
+        <v>1.47</v>
+      </c>
+      <c r="D41" s="21">
+        <v>28</v>
+      </c>
+      <c r="E41" s="21">
+        <f t="shared" si="3"/>
+        <v>41.16</v>
+      </c>
+      <c r="F41" s="24">
+        <f t="shared" si="4"/>
+        <v>45.901013466611133</v>
+      </c>
+      <c r="G41" s="25">
+        <v>2</v>
+      </c>
+      <c r="H41" s="24">
+        <f t="shared" si="5"/>
+        <v>91.802026933222265</v>
+      </c>
+      <c r="I41" s="24">
+        <f t="shared" si="6"/>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="J41" s="30">
+        <v>2.75</v>
+      </c>
+      <c r="K41" s="20">
+        <v>600</v>
+      </c>
+      <c r="L41" s="20">
+        <v>1700</v>
+      </c>
+      <c r="M41" s="27">
+        <f t="shared" si="10"/>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="N41" s="28">
+        <f t="shared" si="8"/>
+        <v>2.7666215315527349</v>
+      </c>
+      <c r="O41" s="31">
+        <v>2.8</v>
+      </c>
+      <c r="P41" s="29">
+        <f t="shared" si="9"/>
+        <v>-1.192088158830884</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A42" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B42" s="20">
+        <v>230</v>
+      </c>
+      <c r="C42" s="20">
+        <v>1.47</v>
+      </c>
+      <c r="D42" s="21">
+        <v>28</v>
+      </c>
+      <c r="E42" s="21">
+        <f t="shared" si="3"/>
+        <v>41.16</v>
+      </c>
+      <c r="F42" s="24">
+        <f t="shared" si="4"/>
+        <v>45.901013466611133</v>
+      </c>
+      <c r="G42" s="25">
+        <v>2</v>
+      </c>
+      <c r="H42" s="24">
+        <f t="shared" si="5"/>
+        <v>91.802026933222265</v>
+      </c>
+      <c r="I42" s="24">
+        <f t="shared" si="6"/>
+        <v>12.566370614359172</v>
+      </c>
+      <c r="J42" s="30">
+        <v>2.58</v>
+      </c>
+      <c r="K42" s="20">
+        <v>600</v>
+      </c>
+      <c r="L42" s="20">
+        <v>1700</v>
+      </c>
+      <c r="M42" s="27">
+        <f t="shared" si="10"/>
+        <v>1.0414538748281612</v>
+      </c>
+      <c r="N42" s="28">
+        <f t="shared" si="8"/>
+        <v>2.9489182991356668</v>
+      </c>
+      <c r="O42" s="31">
+        <v>3</v>
+      </c>
+      <c r="P42" s="29">
+        <f t="shared" si="9"/>
+        <v>-1.7027233621444426</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
